--- a/Plates/nitrite_key.xlsx
+++ b/Plates/nitrite_key.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E48AFD9-AAD4-774B-B2D2-33BFB956FC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F05521-A3F1-DD46-9CAF-9443BFB22498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="660" windowWidth="17280" windowHeight="21680" activeTab="5" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
     <sheet name="06122026_1" sheetId="3" r:id="rId2"/>
     <sheet name="06172026_1" sheetId="4" r:id="rId3"/>
-    <sheet name="06182026_1" sheetId="5" r:id="rId4"/>
-    <sheet name="06192026_1" sheetId="6" r:id="rId5"/>
-    <sheet name="06222026_1" sheetId="7" r:id="rId6"/>
+    <sheet name="06192026_1" sheetId="6" r:id="rId4"/>
+    <sheet name="06222026_1" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="54">
   <si>
     <t>A</t>
   </si>
@@ -176,6 +175,36 @@
   </si>
   <si>
     <t>gcp-06192026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06212026</t>
+  </si>
+  <si>
+    <t>heron-map_06212026</t>
+  </si>
+  <si>
+    <t>elm-school_06212026</t>
+  </si>
+  <si>
+    <t>heron-out_06212026</t>
+  </si>
+  <si>
+    <t>adams-in_06212026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_06212026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_06212026</t>
+  </si>
+  <si>
+    <t>adams-out_06212026</t>
+  </si>
+  <si>
+    <t>gcp_06212026</t>
+  </si>
+  <si>
+    <t>heron-resi_06212026</t>
   </si>
 </sst>
 </file>
@@ -217,11 +246,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,22 +785,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E2:G2"/>
@@ -787,6 +801,22 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1000,262 +1030,6 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BFC44E5-2276-48CB-9BB8-3B534A9C8A13}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1301,13 +1075,12 @@
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="K9:M9"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8EC54A-B9A9-4952-A34A-AFB7D4777943}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BFC44E5-2276-48CB-9BB8-3B534A9C8A13}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1353,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1362,17 +1135,21 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1381,7 +1158,9 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1391,7 +1170,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1400,7 +1179,9 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1410,7 +1191,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1419,7 +1200,9 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1429,7 +1212,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1438,7 +1221,9 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1448,7 +1233,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1457,7 +1242,9 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1467,7 +1254,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1476,7 +1263,9 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1486,7 +1275,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1495,7 +1284,9 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1507,271 +1298,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC9865D-6389-49D2-ADED-37C31D2A29D8}">
-  <dimension ref="A1:M1048576"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-    <row r="1048576" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E1048576" s="1"/>
-      <c r="F1048576" s="1"/>
-      <c r="G1048576" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="E1048576:G1048576"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="H8:J8"/>
@@ -1810,13 +1336,322 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC9865D-6389-49D2-ADED-37C31D2A29D8}">
+  <dimension ref="A1:M1048576"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="1048576" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E1048576" s="1"/>
+      <c r="F1048576" s="1"/>
+      <c r="G1048576" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1048576:G1048576"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251E4F7D-A0F6-8344-BA0B-7C9516B685C2}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -1861,189 +1696,229 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2187,18 +2062,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2220,14 +2095,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A12E62EB-4C13-40F4-82AA-4D1604D83A1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -2241,4 +2108,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plates/nitrite_key.xlsx
+++ b/Plates/nitrite_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F05521-A3F1-DD46-9CAF-9443BFB22498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F686D314-1396-F04A-B1ED-1843837827DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="1300" yWindow="700" windowWidth="34560" windowHeight="21680" activeTab="4" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="54">
   <si>
     <t>A</t>
   </si>
@@ -785,6 +785,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E2:G2"/>
@@ -801,22 +817,6 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -828,8 +828,10 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -874,207 +876,241 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="I2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1086,6 +1122,8 @@
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -1130,207 +1168,241 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="F9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1389,245 +1461,203 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
     </row>
     <row r="1048576" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E1048576" s="1"/>
@@ -1696,13 +1726,13 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
@@ -1723,21 +1753,18 @@
       <c r="J2" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
@@ -1758,21 +1785,18 @@
       <c r="J3" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
@@ -1784,21 +1808,18 @@
       <c r="G4" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
@@ -1810,21 +1831,18 @@
       <c r="G5" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6" t="s">
@@ -1836,21 +1854,18 @@
       <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
@@ -1862,21 +1877,18 @@
       <c r="G7" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
@@ -1888,21 +1900,18 @@
       <c r="G8" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
       <c r="E9" t="s">
@@ -1914,9 +1923,6 @@
       <c r="G9" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1924,6 +1930,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -2061,35 +2082,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF451231-11C1-40DC-B808-D626057CF16F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2111,9 +2107,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF451231-11C1-40DC-B808-D626057CF16F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plates/nitrite_key.xlsx
+++ b/Plates/nitrite_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F686D314-1396-F04A-B1ED-1843837827DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783EFC5F-6A11-6949-B678-0539DA72747A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="700" windowWidth="34560" windowHeight="21680" activeTab="4" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="5" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="06172026_1" sheetId="4" r:id="rId3"/>
     <sheet name="06192026_1" sheetId="6" r:id="rId4"/>
     <sheet name="06222026_1" sheetId="7" r:id="rId5"/>
+    <sheet name="08032026_1" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="64">
   <si>
     <t>A</t>
   </si>
@@ -205,13 +206,43 @@
   </si>
   <si>
     <t>heron-resi_06212026</t>
+  </si>
+  <si>
+    <t>gcp_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_07312026</t>
+  </si>
+  <si>
+    <t>heron-map_07312026</t>
+  </si>
+  <si>
+    <t>elm-bridge_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_07312026</t>
+  </si>
+  <si>
+    <t>heron-out_07312026</t>
+  </si>
+  <si>
+    <t>elm-school_07312026</t>
+  </si>
+  <si>
+    <t>adams-out_07312026</t>
+  </si>
+  <si>
+    <t>adams-in_07312026</t>
+  </si>
+  <si>
+    <t>heron-resi_07312026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -221,6 +252,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -248,10 +286,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,153 +673,153 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -876,239 +914,194 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1168,239 +1161,194 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1660,9 +1608,9 @@
       </c>
     </row>
     <row r="1048576" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E1048576" s="1"/>
-      <c r="F1048576" s="1"/>
-      <c r="G1048576" s="1"/>
+      <c r="E1048576" s="2"/>
+      <c r="F1048576" s="2"/>
+      <c r="G1048576" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1929,22 +1877,352 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E25759-2FE6-3349-A8F3-D6FDD945E6C2}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -2082,31 +2360,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A12E62EB-4C13-40F4-82AA-4D1604D83A1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF451231-11C1-40DC-B808-D626057CF16F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2122,4 +2391,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A12E62EB-4C13-40F4-82AA-4D1604D83A1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plates/nitrite_key.xlsx
+++ b/Plates/nitrite_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783EFC5F-6A11-6949-B678-0539DA72747A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24F2401-53DC-E149-8752-59CEE25ED7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="5" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="6" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="06192026_1" sheetId="6" r:id="rId4"/>
     <sheet name="06222026_1" sheetId="7" r:id="rId5"/>
     <sheet name="08032026_1" sheetId="8" r:id="rId6"/>
+    <sheet name="08052026_1" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="74">
   <si>
     <t>A</t>
   </si>
@@ -236,6 +237,36 @@
   </si>
   <si>
     <t>heron-resi_07312026</t>
+  </si>
+  <si>
+    <t>gcp_08052026</t>
+  </si>
+  <si>
+    <t>heron-map_08052026</t>
+  </si>
+  <si>
+    <t>elm-bridge_08052026</t>
+  </si>
+  <si>
+    <t>heron-out_08052026</t>
+  </si>
+  <si>
+    <t>elm-school_08052026</t>
+  </si>
+  <si>
+    <t>adams-in_08052026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_08052026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_08052026</t>
+  </si>
+  <si>
+    <t>adams-out_08052026</t>
+  </si>
+  <si>
+    <t>heron-resi_08052026</t>
   </si>
 </sst>
 </file>
@@ -823,22 +854,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E2:G2"/>
@@ -855,6 +870,22 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2222,7 +2253,313 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3594377-4B41-7543-B697-7D578DCB07C8}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -2360,15 +2697,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2376,6 +2704,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF451231-11C1-40DC-B808-D626057CF16F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2389,14 +2725,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE035F8-D68E-4C69-8A9A-AC5006D01AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
